--- a/FOMS.xlsx
+++ b/FOMS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cdepaor2\Desktop\ORLA_Lander_Mission_Architecture\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8C8CE6E-C884-4FF7-8C82-82B8D2333042}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1AE4056-D25F-4C08-8B32-54772DC3C627}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8178484C-9A59-408C-9061-605DB68B52FF}"/>
   </bookViews>
@@ -478,9 +478,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -493,9 +492,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -524,9 +520,9 @@
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -886,41 +882,38 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59353462-C63A-4E9A-8D19-091AF6DE4468}">
   <dimension ref="B1:M13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="30.7109375" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" customWidth="1"/>
-    <col min="5" max="5" width="18.85546875" customWidth="1"/>
-    <col min="6" max="6" width="17.7109375" customWidth="1"/>
-    <col min="7" max="7" width="17.85546875" customWidth="1"/>
-    <col min="8" max="8" width="19.140625" customWidth="1"/>
-    <col min="12" max="12" width="31.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.6640625" customWidth="1"/>
+    <col min="4" max="4" width="18.33203125" customWidth="1"/>
+    <col min="5" max="5" width="18.88671875" customWidth="1"/>
+    <col min="6" max="6" width="17.6640625" customWidth="1"/>
+    <col min="7" max="7" width="17.88671875" customWidth="1"/>
+    <col min="8" max="8" width="19.109375" customWidth="1"/>
+    <col min="12" max="12" width="31.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-    </row>
-    <row r="2" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="9" t="s">
+    <row r="1" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G2" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="H2" s="11" t="s">
         <v>17</v>
       </c>
       <c r="L2" t="s">
@@ -930,29 +923,29 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B3" s="5" t="s">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="14">
+      <c r="D3" s="12">
         <v>420000000</v>
       </c>
-      <c r="E3" s="14">
+      <c r="E3" s="12">
         <f>590450605+595702672</f>
         <v>1186153277</v>
       </c>
-      <c r="F3" s="14">
+      <c r="F3" s="12">
         <f>619977909+623175657</f>
         <v>1243153566</v>
       </c>
-      <c r="G3" s="14">
+      <c r="G3" s="12">
         <f>439263260+427249723</f>
         <v>866512983</v>
       </c>
-      <c r="H3" s="15">
+      <c r="H3" s="13">
         <f>140770574+574486153</f>
         <v>715256727</v>
       </c>
@@ -960,30 +953,30 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B4" s="7" t="s">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B4" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="16">
+      <c r="D4" s="14">
         <f>D11/20</f>
         <v>38929794.399999999</v>
       </c>
-      <c r="E4" s="16">
+      <c r="E4" s="14">
         <f t="shared" ref="E4:H4" si="0">E11/20</f>
         <v>38929794.408983096</v>
       </c>
-      <c r="F4" s="16">
+      <c r="F4" s="14">
         <f t="shared" si="0"/>
         <v>38929794.408983096</v>
       </c>
-      <c r="G4" s="28">
+      <c r="G4" s="26">
         <f t="shared" si="0"/>
         <v>38929794.408983096</v>
       </c>
-      <c r="H4" s="29">
+      <c r="H4" s="27">
         <f t="shared" si="0"/>
         <v>70494492.577562004</v>
       </c>
@@ -991,30 +984,30 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B5" s="7" t="s">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B5" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="16">
+      <c r="D5" s="14">
         <f>D4/40000</f>
         <v>973.24486000000002</v>
       </c>
-      <c r="E5" s="16">
+      <c r="E5" s="14">
         <f t="shared" ref="E5:H5" si="1">E4/40000</f>
         <v>973.24486022457745</v>
       </c>
-      <c r="F5" s="16">
+      <c r="F5" s="14">
         <f t="shared" si="1"/>
         <v>973.24486022457745</v>
       </c>
-      <c r="G5" s="28">
+      <c r="G5" s="26">
         <f t="shared" si="1"/>
         <v>973.24486022457745</v>
       </c>
-      <c r="H5" s="29">
+      <c r="H5" s="27">
         <f t="shared" si="1"/>
         <v>1762.3623144390501</v>
       </c>
@@ -1022,30 +1015,30 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B6" s="7" t="s">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B6" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="16">
+      <c r="D6" s="14">
         <f>D4/40000</f>
         <v>973.24486000000002</v>
       </c>
-      <c r="E6" s="16">
+      <c r="E6" s="14">
         <f t="shared" ref="E6:H6" si="2">E4/40000</f>
         <v>973.24486022457745</v>
       </c>
-      <c r="F6" s="16">
+      <c r="F6" s="14">
         <f t="shared" si="2"/>
         <v>973.24486022457745</v>
       </c>
-      <c r="G6" s="28">
+      <c r="G6" s="26">
         <f t="shared" si="2"/>
         <v>973.24486022457745</v>
       </c>
-      <c r="H6" s="29">
+      <c r="H6" s="27">
         <f t="shared" si="2"/>
         <v>1762.3623144390501</v>
       </c>
@@ -1053,143 +1046,143 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B7" s="7" t="s">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B7" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="16"/>
-      <c r="H7" s="17"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="15"/>
       <c r="M7" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B8" s="20" t="s">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B8" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="C8" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="22">
+      <c r="D8" s="20">
         <v>2000</v>
       </c>
-      <c r="E8" s="22">
+      <c r="E8" s="20">
         <v>2000</v>
       </c>
-      <c r="F8" s="22">
+      <c r="F8" s="20">
         <v>2000</v>
       </c>
-      <c r="G8" s="22">
+      <c r="G8" s="20">
         <v>2000</v>
       </c>
-      <c r="H8" s="23">
+      <c r="H8" s="21">
         <v>2000</v>
       </c>
       <c r="M8" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="24" t="s">
+    <row r="9" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="25" t="s">
+      <c r="C9" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="26">
+      <c r="D9" s="24">
         <v>2000</v>
       </c>
-      <c r="E9" s="26">
+      <c r="E9" s="24">
         <v>2000</v>
       </c>
-      <c r="F9" s="26">
+      <c r="F9" s="24">
         <v>2000</v>
       </c>
-      <c r="G9" s="26">
+      <c r="G9" s="24">
         <v>2000</v>
       </c>
-      <c r="H9" s="27">
+      <c r="H9" s="25">
         <v>2000</v>
       </c>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B10" s="2" t="s">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B10" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="18">
+      <c r="D10" s="16">
         <v>1198651141</v>
       </c>
-      <c r="E10" s="18">
+      <c r="E10" s="16">
         <v>1964749166</v>
       </c>
-      <c r="F10" s="18">
+      <c r="F10" s="16">
         <v>2021749454</v>
       </c>
-      <c r="G10" s="18">
+      <c r="G10" s="16">
         <v>1645108871</v>
       </c>
-      <c r="H10" s="18">
+      <c r="H10" s="16">
         <v>2125146579</v>
       </c>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B11" s="2" t="s">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B11" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="18">
+      <c r="D11" s="16">
         <v>778595888</v>
       </c>
-      <c r="E11" s="18">
+      <c r="E11" s="16">
         <v>778595888.17966199</v>
       </c>
-      <c r="F11" s="18">
+      <c r="F11" s="16">
         <v>778595888.17966199</v>
       </c>
-      <c r="G11" s="18">
+      <c r="G11" s="16">
         <v>778595888.17966199</v>
       </c>
-      <c r="H11" s="18">
+      <c r="H11" s="16">
         <v>1409889851.55124</v>
       </c>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B12" s="19" t="s">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B12" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="3">
         <f>D10/40000</f>
         <v>29966.278525000002</v>
       </c>
-      <c r="E12" s="4">
+      <c r="E12" s="3">
         <f t="shared" ref="E12:H12" si="3">E10/40000</f>
         <v>49118.729149999999</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F12" s="3">
         <f t="shared" si="3"/>
         <v>50543.736349999999</v>
       </c>
-      <c r="G12" s="4">
+      <c r="G12" s="3">
         <f t="shared" si="3"/>
         <v>41127.721774999998</v>
       </c>
-      <c r="H12" s="4">
+      <c r="H12" s="3">
         <f t="shared" si="3"/>
         <v>53128.664474999998</v>
       </c>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>29</v>
       </c>
